--- a/UNIT_ECONOMICS.xlsx
+++ b/UNIT_ECONOMICS.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>소규모 사업자 프로그램 15% 가정. 정산 화면에서 실제 적용률 확인 필요</t>
+          <t>소규모 사업자 프로그램 15% 가입 완료(2026-10-08 메모 기준). 실제 적용률은 정산 화면에서 확인 필요(사용자)</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>가정: 현재 구간 무료. 요금제 확인 필요</t>
+          <t>RevenueCat 공식 요금 페이지(2026-10-20 확인): 월 추적 매출(MTR) $2,500까지 무료, 도달 후 1%. 지금 규모는 0 유지. 1% 적용 범위(전체/초과분)는 페이지에 불명확</t>
         </is>
       </c>
     </row>

--- a/UNIT_ECONOMICS.xlsx
+++ b/UNIT_ECONOMICS.xlsx
@@ -12,6 +12,7 @@
     <sheet name="90일 시나리오" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="CPI 민감도" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="500만원 목표" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="1개월 목표" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="$#,##0.00;($#,##0.00);-"/>
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);-"/>
     <numFmt numFmtId="166" formatCode="$0.0000"/>
@@ -29,6 +30,7 @@
     <numFmt numFmtId="169" formatCode="$#,##0;($#,##0);-"/>
     <numFmt numFmtId="170" formatCode="0.000"/>
     <numFmt numFmtId="171" formatCode="0.0000"/>
+    <numFmt numFmtId="172" formatCode="₩#,##0;(₩#,##0);-"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -113,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -152,6 +154,17 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2680,4 +2693,1427 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>1개월 목표: 첫 달 월 총매출 500만원에 필요한 설치·조회수 (해외·한국·혼합)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>총매출 = 사용자가 낸 돈(한국은 부가세 포함가). 첫 달에는 연간 구독료가 한 번에 잡혀 부풀어 보이므로, 매달 유지되는 수준은 "정상 상태" 줄을 본다. 파란 글씨 = 입력, 노란 칸 = 확인이 필요한 가정. 2026-10-27 작성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B4" s="34" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="inlineStr">
+        <is>
+          <t>출처 / 상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>목표 월 총매출 (원)</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>사용자 목표 (2026-10-27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>환율 (원/달러)</t>
+        </is>
+      </c>
+      <c r="B6" s="35">
+        <f>'500만원 목표'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>500만원 목표 탭의 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>목표 월 총매출 (달러)</t>
+        </is>
+      </c>
+      <c r="B7" s="20">
+        <f>B5/B6</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>스토어 수수료율</t>
+        </is>
+      </c>
+      <c r="B8" s="36">
+        <f>입력!$B$9</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>입력 탭</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>환불·취소 손실률</t>
+        </is>
+      </c>
+      <c r="B9" s="36">
+        <f>입력!$B$10</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>입력 탭</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>RevenueCat 수수료율</t>
+        </is>
+      </c>
+      <c r="B10" s="36">
+        <f>입력!$B$11</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>입력 탭</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>한국 부가세율</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>한국 스토어 표시가는 부가세 10% 포함, 스토어가 대신 납부한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>해외 실수령 비율 (총매출 대비)</t>
+        </is>
+      </c>
+      <c r="B12" s="37">
+        <f>(1-B8)*(1-B9)*(1-B10)</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>수수료·환불·RevenueCat 차감</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>한국 실수령 비율 (총매출 대비)</t>
+        </is>
+      </c>
+      <c r="B13" s="37">
+        <f>B12/(1+B11)</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>부가세를 먼저 빼고 같은 차감</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>조회→설치 전환율</t>
+        </is>
+      </c>
+      <c r="B14" s="38">
+        <f>'500만원 목표'!$B$29</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>500만원 목표 탭의 가정(출처 없음). 첫 영상 데이터로 교체</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>설치당 AI 비용 ($)</t>
+        </is>
+      </c>
+      <c r="B15" s="39">
+        <f>사용자당!$B$4</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>사용자당 탭</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>해외 ($)</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>한국 (원)</t>
+        </is>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>출처 / 상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>월 구독</t>
+        </is>
+      </c>
+      <c r="B18" s="40">
+        <f>입력!$B$6</f>
+        <v/>
+      </c>
+      <c r="C18" s="41" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>해외: 입력 탭. 한국: 스토어 자동 환산 근사(가정). 콘솔 실제가로 교체</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>연간 구독</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="C19" s="41" t="n">
+        <v>69000</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>해외: 앱 페이월 연간 플랜(스토어 표시 월 $4.16). 한국: 근사(가정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>딥 리포트</t>
+        </is>
+      </c>
+      <c r="B20" s="40">
+        <f>입력!$B$7</f>
+        <v/>
+      </c>
+      <c r="C20" s="41" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>해외: 입력 탭. 한국: 근사(가정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>궁합 리포트</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="C21" s="41" t="n">
+        <v>9900</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>IAP_PRODUCTS.md "$6.99 가정", 한국: 근사(가정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>해외 보수</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>해외 중간</t>
+        </is>
+      </c>
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>해외 좋음</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="inlineStr">
+        <is>
+          <t>한국 보수</t>
+        </is>
+      </c>
+      <c r="F23" s="34" t="inlineStr">
+        <is>
+          <t>한국 중간</t>
+        </is>
+      </c>
+      <c r="G23" s="34" t="inlineStr">
+        <is>
+          <t>한국 좋음</t>
+        </is>
+      </c>
+      <c r="H23" s="34" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>입력 (전부 추정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>설치→구독 전환율 (첫 달)</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>RevenueCat 2026 중앙값 2.0%(확인됨) 주변. 한국은 건별 결제 선호를 가정해 조금 낮게</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>구독 중 연간 비중</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>설치→딥 리포트 구매율</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G27" s="17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>추정. 한국은 건별 결제(복채) 관행으로 높게</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>설치→궁합 리포트 구매율</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>구독자 월 이탈률 (정상 상태용)</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>500만원 목표 탭과 같은 값 (근거 약함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>첫 달 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>첫 결제 평균 (해외 $ / 한국 원)</t>
+        </is>
+      </c>
+      <c r="B31" s="15">
+        <f>B26*$B$19+(1-B26)*$B$18</f>
+        <v/>
+      </c>
+      <c r="C31" s="15">
+        <f>C26*$B$19+(1-C26)*$B$18</f>
+        <v/>
+      </c>
+      <c r="D31" s="15">
+        <f>D26*$B$19+(1-D26)*$B$18</f>
+        <v/>
+      </c>
+      <c r="E31" s="42">
+        <f>E26*$C$19+(1-E26)*$C$18</f>
+        <v/>
+      </c>
+      <c r="F31" s="42">
+        <f>F26*$C$19+(1-F26)*$C$18</f>
+        <v/>
+      </c>
+      <c r="G31" s="42">
+        <f>G26*$C$19+(1-G26)*$C$18</f>
+        <v/>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>연간 비중으로 월·연간 가중</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>설치당 첫 달 총매출 (해외 $ / 한국 원)</t>
+        </is>
+      </c>
+      <c r="B32" s="15">
+        <f>B25*B31+B27*$B$20+B28*$B$21</f>
+        <v/>
+      </c>
+      <c r="C32" s="15">
+        <f>C25*C31+C27*$B$20+C28*$B$21</f>
+        <v/>
+      </c>
+      <c r="D32" s="15">
+        <f>D25*D31+D27*$B$20+D28*$B$21</f>
+        <v/>
+      </c>
+      <c r="E32" s="42">
+        <f>E25*E31+E27*$C$20+E28*$C$21</f>
+        <v/>
+      </c>
+      <c r="F32" s="42">
+        <f>F25*F31+F27*$C$20+F28*$C$21</f>
+        <v/>
+      </c>
+      <c r="G32" s="42">
+        <f>G25*G31+G27*$C$20+G28*$C$21</f>
+        <v/>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>구독 + 딥 리포트 + 궁합</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>설치당 첫 달 총매출 (다른 통화 환산: 해외→원, 한국→$)</t>
+        </is>
+      </c>
+      <c r="B33" s="42">
+        <f>B32*$B$6</f>
+        <v/>
+      </c>
+      <c r="C33" s="42">
+        <f>C32*$B$6</f>
+        <v/>
+      </c>
+      <c r="D33" s="42">
+        <f>D32*$B$6</f>
+        <v/>
+      </c>
+      <c r="E33" s="15">
+        <f>E32/$B$6</f>
+        <v/>
+      </c>
+      <c r="F33" s="15">
+        <f>F32/$B$6</f>
+        <v/>
+      </c>
+      <c r="G33" s="15">
+        <f>G32/$B$6</f>
+        <v/>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>필요 월 설치</t>
+        </is>
+      </c>
+      <c r="B34" s="19">
+        <f>$B$7/B32</f>
+        <v/>
+      </c>
+      <c r="C34" s="19">
+        <f>$B$7/C32</f>
+        <v/>
+      </c>
+      <c r="D34" s="19">
+        <f>$B$7/D32</f>
+        <v/>
+      </c>
+      <c r="E34" s="19">
+        <f>$B$5/E32</f>
+        <v/>
+      </c>
+      <c r="F34" s="19">
+        <f>$B$5/F32</f>
+        <v/>
+      </c>
+      <c r="G34" s="19">
+        <f>$B$5/G32</f>
+        <v/>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>목표 총매출 ÷ 설치당 총매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>필요 일 설치</t>
+        </is>
+      </c>
+      <c r="B35" s="19">
+        <f>B34/30</f>
+        <v/>
+      </c>
+      <c r="C35" s="19">
+        <f>C34/30</f>
+        <v/>
+      </c>
+      <c r="D35" s="19">
+        <f>D34/30</f>
+        <v/>
+      </c>
+      <c r="E35" s="19">
+        <f>E34/30</f>
+        <v/>
+      </c>
+      <c r="F35" s="19">
+        <f>F34/30</f>
+        <v/>
+      </c>
+      <c r="G35" s="19">
+        <f>G34/30</f>
+        <v/>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>첫 달 신규 구독자</t>
+        </is>
+      </c>
+      <c r="B36" s="19">
+        <f>B34*B25</f>
+        <v/>
+      </c>
+      <c r="C36" s="19">
+        <f>C34*C25</f>
+        <v/>
+      </c>
+      <c r="D36" s="19">
+        <f>D34*D25</f>
+        <v/>
+      </c>
+      <c r="E36" s="19">
+        <f>E34*E25</f>
+        <v/>
+      </c>
+      <c r="F36" s="19">
+        <f>F34*F25</f>
+        <v/>
+      </c>
+      <c r="G36" s="19">
+        <f>G34*G25</f>
+        <v/>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>첫 달 리포트 판매 (딥+궁합)</t>
+        </is>
+      </c>
+      <c r="B37" s="19">
+        <f>B34*(B27+B28)</f>
+        <v/>
+      </c>
+      <c r="C37" s="19">
+        <f>C34*(C27+C28)</f>
+        <v/>
+      </c>
+      <c r="D37" s="19">
+        <f>D34*(D27+D28)</f>
+        <v/>
+      </c>
+      <c r="E37" s="19">
+        <f>E34*(E27+E28)</f>
+        <v/>
+      </c>
+      <c r="F37" s="19">
+        <f>F34*(F27+F28)</f>
+        <v/>
+      </c>
+      <c r="G37" s="19">
+        <f>G34*(G27+G28)</f>
+        <v/>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>필요 월 조회수 (전부 숏폼 유입일 때)</t>
+        </is>
+      </c>
+      <c r="B38" s="19">
+        <f>B34/$B$14</f>
+        <v/>
+      </c>
+      <c r="C38" s="19">
+        <f>C34/$B$14</f>
+        <v/>
+      </c>
+      <c r="D38" s="19">
+        <f>D34/$B$14</f>
+        <v/>
+      </c>
+      <c r="E38" s="19">
+        <f>E34/$B$14</f>
+        <v/>
+      </c>
+      <c r="F38" s="19">
+        <f>F34/$B$14</f>
+        <v/>
+      </c>
+      <c r="G38" s="19">
+        <f>G34/$B$14</f>
+        <v/>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>조회→설치 전환율 가정</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>실제 손에 들어오는 돈 (원)</t>
+        </is>
+      </c>
+      <c r="B39" s="42">
+        <f>$B$5*$B$12</f>
+        <v/>
+      </c>
+      <c r="C39" s="42">
+        <f>$B$5*$B$12</f>
+        <v/>
+      </c>
+      <c r="D39" s="42">
+        <f>$B$5*$B$12</f>
+        <v/>
+      </c>
+      <c r="E39" s="42">
+        <f>$B$5*$B$13</f>
+        <v/>
+      </c>
+      <c r="F39" s="42">
+        <f>$B$5*$B$13</f>
+        <v/>
+      </c>
+      <c r="G39" s="42">
+        <f>$B$5*$B$13</f>
+        <v/>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>총매출 × 실수령 비율</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>정상 상태 (매달 같은 설치가 계속 들어올 때)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>설치 1건/월당 월 총매출</t>
+        </is>
+      </c>
+      <c r="B41" s="15">
+        <f>B25*(1-B26)*$B$18/B29+B25*B26*$B$19+B27*$B$20+B28*$B$21</f>
+        <v/>
+      </c>
+      <c r="C41" s="15">
+        <f>C25*(1-C26)*$B$18/C29+C25*C26*$B$19+C27*$B$20+C28*$B$21</f>
+        <v/>
+      </c>
+      <c r="D41" s="15">
+        <f>D25*(1-D26)*$B$18/D29+D25*D26*$B$19+D27*$B$20+D28*$B$21</f>
+        <v/>
+      </c>
+      <c r="E41" s="42">
+        <f>E25*(1-E26)*$C$18/E29+E25*E26*$C$19+E27*$C$20+E28*$C$21</f>
+        <v/>
+      </c>
+      <c r="F41" s="42">
+        <f>F25*(1-F26)*$C$18/F29+F25*F26*$C$19+F27*$C$20+F28*$C$21</f>
+        <v/>
+      </c>
+      <c r="G41" s="42">
+        <f>G25*(1-G26)*$C$18/G29+G25*G26*$C$19+G27*$C$20+G28*$C$21</f>
+        <v/>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>월 구독자는 1/이탈률 개월 유지. 연간 구독료는 들어온 달에 현금으로 잡음, 갱신은 무시</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>필요 월 설치 (정상 상태)</t>
+        </is>
+      </c>
+      <c r="B42" s="19">
+        <f>$B$7/B41</f>
+        <v/>
+      </c>
+      <c r="C42" s="19">
+        <f>$B$7/C41</f>
+        <v/>
+      </c>
+      <c r="D42" s="19">
+        <f>$B$7/D41</f>
+        <v/>
+      </c>
+      <c r="E42" s="19">
+        <f>$B$5/E41</f>
+        <v/>
+      </c>
+      <c r="F42" s="19">
+        <f>$B$5/F41</f>
+        <v/>
+      </c>
+      <c r="G42" s="19">
+        <f>$B$5/G41</f>
+        <v/>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>유지되는 월 구독자 수</t>
+        </is>
+      </c>
+      <c r="B43" s="19">
+        <f>B42*B25*(1-B26)/B29</f>
+        <v/>
+      </c>
+      <c r="C43" s="19">
+        <f>C42*C25*(1-C26)/C29</f>
+        <v/>
+      </c>
+      <c r="D43" s="19">
+        <f>D42*D25*(1-D26)/D29</f>
+        <v/>
+      </c>
+      <c r="E43" s="19">
+        <f>E42*E25*(1-E26)/E29</f>
+        <v/>
+      </c>
+      <c r="F43" s="19">
+        <f>F42*F25*(1-F26)/F29</f>
+        <v/>
+      </c>
+      <c r="G43" s="19">
+        <f>G42*G25*(1-G26)/G29</f>
+        <v/>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="34" t="inlineStr">
+        <is>
+          <t>기준값</t>
+        </is>
+      </c>
+      <c r="B45" s="34" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C45" s="34" t="inlineStr">
+        <is>
+          <t>출처 / 상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>RevenueCat 60일 설치당 매출 중앙값 ($)</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>RevenueCat State of Subscription Apps 2026 (확인됨, 입력 탭·CPI 민감도 탭과 같은 값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>이 값으로 필요한 해외 월 설치</t>
+        </is>
+      </c>
+      <c r="B47" s="19">
+        <f>$B$7/B46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t>혼합 (한국 + 해외)</t>
+        </is>
+      </c>
+      <c r="B49" s="34" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C49" s="34" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>한국에서 내는 매출 비중</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>한국 필요 월 설치 (한국 중간)</t>
+        </is>
+      </c>
+      <c r="B51" s="19">
+        <f>$B$5*B50/$F$32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>해외 필요 월 설치 (해외 중간)</t>
+        </is>
+      </c>
+      <c r="B52" s="19">
+        <f>$B$7*(1-B50)/$C$32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>해외 필요 월 설치 (RevenueCat 중앙값)</t>
+        </is>
+      </c>
+      <c r="B53" s="19">
+        <f>$B$7*(1-B50)/$B$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>합계 (해외 중간)</t>
+        </is>
+      </c>
+      <c r="B54" s="19">
+        <f>B51+B52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>합계 (해외 RevenueCat 중앙값)</t>
+        </is>
+      </c>
+      <c r="B55" s="19">
+        <f>B51+B53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>실제 손에 들어오는 돈 (원)</t>
+        </is>
+      </c>
+      <c r="B56" s="42">
+        <f>$B$5*(B50*$B$13+(1-B50)*$B$12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
+          <t>유료 광고로 채울 때</t>
+        </is>
+      </c>
+      <c r="B58" s="34" t="inlineStr">
+        <is>
+          <t>해외 CPI ($)</t>
+        </is>
+      </c>
+      <c r="C58" s="34" t="inlineStr">
+        <is>
+          <t>해외 광고비 ($)</t>
+        </is>
+      </c>
+      <c r="D58" s="34" t="inlineStr">
+        <is>
+          <t>해외 첫 달 손익 ($)</t>
+        </is>
+      </c>
+      <c r="E58" s="34" t="inlineStr">
+        <is>
+          <t>한국 CPI (원)</t>
+        </is>
+      </c>
+      <c r="F58" s="34" t="inlineStr">
+        <is>
+          <t>한국 광고비 (원)</t>
+        </is>
+      </c>
+      <c r="G58" s="34" t="inlineStr">
+        <is>
+          <t>한국 첫 달 손익 (원)</t>
+        </is>
+      </c>
+      <c r="H58" s="43" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>단가 1</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="20">
+        <f>$C$34*B59</f>
+        <v/>
+      </c>
+      <c r="D59" s="20">
+        <f>$B$7*$B$12-$C$34*(B59+$B$15)</f>
+        <v/>
+      </c>
+      <c r="E59" s="44" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F59" s="42">
+        <f>$F$34*E59</f>
+        <v/>
+      </c>
+      <c r="G59" s="42">
+        <f>$B$5*$B$13-$F$34*(E59+$B$15*$B$6)</f>
+        <v/>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>설치 전부를 광고로 산다고 가정. 해외는 "해외 중간", 한국은 "한국 중간" 설치당 매출 사용. AI 비용 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>단가 2</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" s="20">
+        <f>$C$34*B60</f>
+        <v/>
+      </c>
+      <c r="D60" s="20">
+        <f>$B$7*$B$12-$C$34*(B60+$B$15)</f>
+        <v/>
+      </c>
+      <c r="E60" s="44" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F60" s="42">
+        <f>$F$34*E60</f>
+        <v/>
+      </c>
+      <c r="G60" s="42">
+        <f>$B$5*$B$13-$F$34*(E60+$B$15*$B$6)</f>
+        <v/>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>CPI는 실측 없음. 해외 일반 벤치마크 iOS $1.5~3.5, 한국 ₩4,000~15,000(블로그, 출처 약함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>단가 3</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" s="20">
+        <f>$C$34*B61</f>
+        <v/>
+      </c>
+      <c r="D61" s="20">
+        <f>$B$7*$B$12-$C$34*(B61+$B$15)</f>
+        <v/>
+      </c>
+      <c r="E61" s="44" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F61" s="42">
+        <f>$F$34*E61</f>
+        <v/>
+      </c>
+      <c r="G61" s="42">
+        <f>$B$5*$B$13-$F$34*(E61+$B$15*$B$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>단가 4</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C62" s="20">
+        <f>$C$34*B62</f>
+        <v/>
+      </c>
+      <c r="D62" s="20">
+        <f>$B$7*$B$12-$C$34*(B62+$B$15)</f>
+        <v/>
+      </c>
+      <c r="E62" s="44" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F62" s="42">
+        <f>$F$34*E62</f>
+        <v/>
+      </c>
+      <c r="G62" s="42">
+        <f>$B$5*$B$13-$F$34*(E62+$B$15*$B$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>손익분기 CPI (이 이하여야 첫 달 흑자)</t>
+        </is>
+      </c>
+      <c r="D63" s="15">
+        <f>$C$32*$B$12-$B$15</f>
+        <v/>
+      </c>
+      <c r="G63" s="42">
+        <f>$F$32*$B$13-$B$15*$B$6</f>
+        <v/>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>해외 중간 / 한국 중간 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="34" t="inlineStr">
+        <is>
+          <t>국내 운세 앱 비교</t>
+        </is>
+      </c>
+      <c r="B65" s="34" t="inlineStr">
+        <is>
+          <t>연 매출 (원)</t>
+        </is>
+      </c>
+      <c r="C65" s="34" t="inlineStr">
+        <is>
+          <t>월간 사용자 (MAU)</t>
+        </is>
+      </c>
+      <c r="D65" s="34" t="inlineStr">
+        <is>
+          <t>MAU당 월 매출 (원)</t>
+        </is>
+      </c>
+      <c r="E65" s="34" t="inlineStr">
+        <is>
+          <t>500만원에 필요한 MAU</t>
+        </is>
+      </c>
+      <c r="F65" s="34" t="inlineStr">
+        <is>
+          <t>신생 앱(절반 수익)일 때</t>
+        </is>
+      </c>
+      <c r="G65" s="34" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>포스텔러 (MAU 낮은 보도)</t>
+        </is>
+      </c>
+      <c r="B66" s="44" t="n">
+        <v>9900000000</v>
+      </c>
+      <c r="C66" s="16" t="n">
+        <v>620000</v>
+      </c>
+      <c r="D66" s="42">
+        <f>B66/12/C66</f>
+        <v/>
+      </c>
+      <c r="E66" s="19">
+        <f>$B$5/D66</f>
+        <v/>
+      </c>
+      <c r="F66" s="19">
+        <f>$B$5/(D66*$B$69)</f>
+        <v/>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>유니콘팩토리 2025-01-24(2023 매출 99억), 한국경제 2026-02-10(MAU 약 62만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>포스텔러 (MAU 높은 보도)</t>
+        </is>
+      </c>
+      <c r="B67" s="44" t="n">
+        <v>9900000000</v>
+      </c>
+      <c r="C67" s="16" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="D67" s="42">
+        <f>B67/12/C67</f>
+        <v/>
+      </c>
+      <c r="E67" s="19">
+        <f>$B$5/D67</f>
+        <v/>
+      </c>
+      <c r="F67" s="19">
+        <f>$B$5/(D67*$B$69)</f>
+        <v/>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>ZDNet Korea 2025-02-03(MAU 140만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>점신</t>
+        </is>
+      </c>
+      <c r="B68" s="44" t="n">
+        <v>5500000000</v>
+      </c>
+      <c r="C68" s="16" t="n">
+        <v>950000</v>
+      </c>
+      <c r="D68" s="42">
+        <f>B68/12/C68</f>
+        <v/>
+      </c>
+      <c r="E68" s="19">
+        <f>$B$5/D68</f>
+        <v/>
+      </c>
+      <c r="F68" s="19">
+        <f>$B$5/(D68*$B$69)</f>
+        <v/>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>유니콘팩토리(2023 50억, 2024 추정 60억의 중간), 탑스타뉴스 2025-02 모바일인덱스(MAU 95만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>신생 앱의 MAU당 매출 비율 (성숙 앱 대비)</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>가정. 근거 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>참고: 12~2월 신년 시즌에 운세 앱 이용자 약 20% 증가 (업계 관계자 발언, 유니콘팩토리 2025-01-24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>출처 URL: unicornfactory.co.kr/article/2025012414570018707 · hankyung.com/article/2026021070861 · zdnet.co.kr/view/?no=20250203104315 · topstarnews.net/news/articleView.html?idxno=15623421 · 238lab.kr/blog-Terms-MKT-CPI</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>